--- a/stories/arbres/ATOM-FAM.SEC.002-02.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lina joue au parc avec papa. Elle est près du bac à sable. Le sable est tiède. Un adulte parle tout bas. Il dit : c'est notre secret. Lina sent son ventre. C'est serré. C'est un malaise. Lina a peur. Lina marche vers papa. Elle prend sa main. Lina dit : papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Papa dit : merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. Même si un adulte parle d'un secret. On va raconter à papa ou maman. Papa reste tout près. Plus tard, ils vont au magasin. Maman est là aussi. Lina sent encore son ventre. Un bruit fort la surprend. Elle a peur. Elle se souvient. Elle marche vers maman. Elle dit : maman, j'ai peur. Maman écoute. Maman dit : tu as repris le geste. Ce qui fait peur se raconte à papa ou maman. Lina se sent plus légère.</t>
+          <t>Lina joue au parc avec papa. Elle est près du bac à sable. Le sable est tiède. Un adulte parle tout bas. C'est notre secret. Lina sent son ventre. C'est serré. C'est un malaise. Lina a peur. Lina marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. Même si un adulte parle d'un secret. On va raconter à papa ou maman. Papa reste tout près. Plus tard, ils vont au magasin. Maman est là aussi. Lina sent encore son ventre. Un bruit fort la surprend. Elle a peur. Elle se souvient. Elle marche vers maman. Maman, j'ai peur. Maman écoute. Tu as repris le geste. Ce qui fait peur se raconte à papa ou maman. Lina se sent plus légère.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lina joue au parc avec papa. Elle est près du bac à sable. Le sable est tiède. Un adulte parle tout bas.
+narrateur|C'est notre secret.
+narrateur|Lina sent son ventre. C'est serré. C'est un malaise. Lina a peur. Lina marche vers papa. Elle prend sa main.
+enfant-f|Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute.
+papa|Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. Même si un adulte parle d'un secret. On va raconter à papa ou maman. Papa reste tout près. Plus tard, ils vont au magasin. Maman est là aussi.
+narrateur|Lina sent encore son ventre. Un bruit fort la surprend. Elle a peur. Elle se souvient. Elle marche vers maman.
+narrateur|Maman, j'ai peur. Maman écoute.
+maman|Tu as repris le geste. Ce qui fait peur se raconte à papa ou maman.
+narrateur|Lina se sent plus légère.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a peur. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a senti le malaise. Elle a marché vers papa, puis vers maman. Elle a raconté. Ce qui fait peur se raconte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1838,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Lina s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2005,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2045,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-02.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,11 @@
 narrateur|Lina se sent plus légère.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1515,7 @@
           <t>narrateur|Lina a peur. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1687,7 @@
           <t>narrateur|Lina a senti le malaise. Elle a marché vers papa, puis vers maman. Elle a raconté. Ce qui fait peur se raconte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1843,6 +1855,7 @@
           <t>narrateur|Lina s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2010,6 +2023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2066,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2281,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.SEC.002-02.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lina raconte sa peur deux fois</t>
+          <t>Mila raconte sa peur deux fois</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une feuille jaune colle à une chaussure. Mila raconte au parc, puis encore au magasin.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lina joue au parc avec papa. Elle est près du bac à sable. Le sable est tiède. Un adulte parle tout bas. C'est notre secret. Lina sent son ventre. C'est serré. C'est un malaise. Lina a peur. Lina marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. Même si un adulte parle d'un secret. On va raconter à papa ou maman. Papa reste tout près. Plus tard, ils vont au magasin. Maman est là aussi. Lina sent encore son ventre. Un bruit fort la surprend. Elle a peur. Elle se souvient. Elle marche vers maman. Maman, j'ai peur. Maman écoute. Tu as repris le geste. Ce qui fait peur se raconte à papa ou maman. Lina se sent plus légère.</t>
+          <t>Une feuille jaune colle à une chaussure. Elle est un peu humide. Une flaque garde un bout de ciel. Un nuage y passe tout lent. Le banc du parc est tiède. Un foulard bleu y dort. La terre mouillée sent fort. Mila, on enlève la feuille ? Elle colle encore. Voilà. Elle est partie. En ce moment, Mila est près du bac. Le sable est frais après la pluie. Elle fait un petit tas. Il est froid, papa. Oui. On reste ensemble. Une voix d'adulte parle tout bas. Mila sent son ventre. Le ventre est serré. C'est un malaise. Mila a peur. Elle laisse le tas de sable. Elle marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. On reste près ? Oui, Mila. Bravo. Tu as fait du bon travail. La feuille jaune s'envole un peu. Plus tard, ils vont au magasin. Le caddie a une roue qui chante. L'air du magasin est un peu froid. Mila, tu tiens ma main ? Oui, maman. Bravo. Un bruit fort claque au fond. Mila sent encore son ventre. Le ventre se serre. Mila a peur. Elle se souvient. Elle marche vers maman. Maman, j'ai peur. Le bruit a été fort. Mon ventre est serré. Merci de raconter. Tu as repris le geste. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je suis là aussi. Je me sens plus légère. Bravo, Mila. Tu as fait du bon travail. La roue du caddie chante encore. Mila serre la main de maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Lina joue au parc avec papa. Elle est près du bac à sable. Le sable est tiède. Un adulte parle tout bas.
-narrateur|C'est notre secret.
-narrateur|Lina sent son ventre. C'est serré. C'est un malaise. Lina a peur. Lina marche vers papa. Elle prend sa main.
-enfant-f|Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute.
-papa|Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. Même si un adulte parle d'un secret. On va raconter à papa ou maman. Papa reste tout près. Plus tard, ils vont au magasin. Maman est là aussi.
-narrateur|Lina sent encore son ventre. Un bruit fort la surprend. Elle a peur. Elle se souvient. Elle marche vers maman.
-narrateur|Maman, j'ai peur. Maman écoute.
-maman|Tu as repris le geste. Ce qui fait peur se raconte à papa ou maman.
-narrateur|Lina se sent plus légère.</t>
+          <t>narrateur|Une feuille jaune colle à une chaussure.
+narrateur|Elle est un peu humide.
+narrateur|Une flaque garde un bout de ciel.
+narrateur|Un nuage y passe tout lent.
+narrateur|Le banc du parc est tiède.
+narrateur|Un foulard bleu y dort.
+narrateur|La terre mouillée sent fort.
+papa|Mila, on enlève la feuille ?
+enfant-f|Elle colle encore.
+papa|Voilà.
+papa|Elle est partie.
+narrateur|En ce moment, Mila est près du bac.
+narrateur|Le sable est frais après la pluie.
+narrateur|Elle fait un petit tas.
+enfant-f|Il est froid, papa.
+papa|Oui.
+papa|On reste ensemble.
+narrateur|Une voix d'adulte parle tout bas.
+narrateur|Mila sent son ventre.
+narrateur|Le ventre est serré.
+narrateur|C'est un malaise.
+narrateur|Mila a peur.
+narrateur|Elle laisse le tas de sable.
+narrateur|Elle marche vers papa.
+narrateur|Elle prend sa main.
+enfant-f|Papa, un adulte a parlé d'un secret.
+enfant-f|Mon ventre est serré.
+enfant-f|J'ai peur.
+papa|Merci de raconter.
+papa|Tu as le droit de le dire.
+papa|Ce qui fait peur se raconte.
+papa|On va raconter à papa ou maman.
+papa|Je reste tout près.
+enfant-f|On reste près ?
+papa|Oui, Mila.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La feuille jaune s'envole un peu.
+narrateur|Plus tard, ils vont au magasin.
+narrateur|Le caddie a une roue qui chante.
+narrateur|L'air du magasin est un peu froid.
+maman|Mila, tu tiens ma main ?
+enfant-f|Oui, maman.
+maman|Bravo.
+narrateur|Un bruit fort claque au fond.
+narrateur|Mila sent encore son ventre.
+narrateur|Le ventre se serre.
+narrateur|Mila a peur.
+narrateur|Elle se souvient.
+narrateur|Elle marche vers maman.
+enfant-f|Maman, j'ai peur.
+enfant-f|Le bruit a été fort.
+enfant-f|Mon ventre est serré.
+maman|Merci de raconter.
+maman|Tu as repris le geste.
+maman|Ce qui fait peur se raconte.
+maman|On va raconter à papa ou maman.
+papa|Je suis là aussi.
+enfant-f|Je me sens plus légère.
+maman|Bravo, Mila.
+maman|Tu as fait du bon travail.
+narrateur|La roue du caddie chante encore.
+narrateur|Mila serre la main de maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1352,7 +1418,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lina a peur. Que fait-elle ?</t>
+          <t>Mila a peur. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1512,7 +1578,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Lina a peur. Que fait-elle ?</t>
+          <t>narrateur|Mila a peur.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1540,7 +1607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lina a senti le malaise. Elle a marché vers papa, puis vers maman. Elle a raconté. Ce qui fait peur se raconte.</t>
+          <t>Mila a senti le malaise. Elle a marché vers papa. Puis vers maman. Elle a raconté. Tu as raconté au parc ? Oui. Et au magasin aussi. Bravo. Ce qui fait peur se raconte. On va raconter à papa ou maman. La feuille jaune n'est plus collée. La main de maman reste chaude.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1684,7 +1751,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Lina a senti le malaise. Elle a marché vers papa, puis vers maman. Elle a raconté. Ce qui fait peur se raconte.</t>
+          <t>narrateur|Mila a senti le malaise.
+narrateur|Elle a marché vers papa.
+narrateur|Puis vers maman.
+narrateur|Elle a raconté.
+papa|Tu as raconté au parc ?
+enfant-f|Oui.
+maman|Et au magasin aussi.
+maman|Bravo.
+papa|Ce qui fait peur se raconte.
+papa|On va raconter à papa ou maman.
+narrateur|La feuille jaune n'est plus collée.
+narrateur|La main de maman reste chaude.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1712,7 +1790,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Lina s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+          <t>Mila s'assoit près de maman. Papa pose un sac tout doux. On a fini les courses. Tu as raconté deux fois. Oui. Au parc, puis ici. Bravo. Tu as fait du bon travail. Le caddie s'arrête. La roue se tait. On rentre maintenant. On se tient la main.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1852,7 +1930,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Lina s'assoit près de maman. Papa est là aussi. Sa main est chaude.</t>
+          <t>narrateur|Mila s'assoit près de maman.
+narrateur|Papa pose un sac tout doux.
+maman|On a fini les courses.
+papa|Tu as raconté deux fois.
+enfant-f|Oui.
+enfant-f|Au parc, puis ici.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le caddie s'arrête.
+narrateur|La roue se tait.
+papa|On rentre maintenant.
+enfant-f|On se tient la main.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1880,7 +1969,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La feuille jaune a séché dehors. J'ai raconté. Bravo, Mila. On t'écoute. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2020,7 +2109,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La feuille jaune a séché dehors.
+enfant-f|J'ai raconté.
+papa|Bravo, Mila.
+maman|On t'écoute.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2042,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2173,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-02.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille jaune colle à une chaussure. Elle est un peu humide. Une flaque garde un bout de ciel. Un nuage y passe tout lent. Le banc du parc est tiède. Un foulard bleu y dort. La terre mouillée sent fort. Mila, on enlève la feuille ? Elle colle encore. Voilà. Elle est partie. En ce moment, Mila est près du bac. Le sable est frais après la pluie. Elle fait un petit tas. Il est froid, papa. Oui. On reste ensemble. Une voix d'adulte parle tout bas. Mila sent son ventre. Le ventre est serré. C'est un malaise. Mila a peur. Elle laisse le tas de sable. Elle marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. On reste près ? Oui, Mila. Bravo. Tu as fait du bon travail. La feuille jaune s'envole un peu. Plus tard, ils vont au magasin. Le caddie a une roue qui chante. L'air du magasin est un peu froid. Mila, tu tiens ma main ? Oui, maman. Bravo. Un bruit fort claque au fond. Mila sent encore son ventre. Le ventre se serre. Mila a peur. Elle se souvient. Elle marche vers maman. Maman, j'ai peur. Le bruit a été fort. Mon ventre est serré. Merci de raconter. Tu as repris le geste. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je suis là aussi. Je me sens plus légère. Bravo, Mila. Tu as fait du bon travail. La roue du caddie chante encore. Mila serre la main de maman.</t>
+          <t>Une feuille jaune colle à une chaussure. Elle est un peu humide. Une flaque garde un bout de ciel. Un nuage y passe tout lent. Le banc du parc est tiède. Un foulard bleu y dort. La terre mouillée sent fort. Mila, on enlève la feuille ? Elle colle encore. Voilà. Elle est partie. En ce moment, Mila est près du bac. Le sable est frais après la pluie. Elle fait un petit tas. Il est froid, papa. Oui. On reste ensemble. Une voix d'adulte parle tout bas. Mila sent son ventre. Le ventre est serré. C'est un malaise. Mila a peur. Elle laisse le tas de sable. Elle marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. On reste près ? Oui, Mila. Bravo. La feuille jaune s'envole un peu. Plus tard, ils vont au magasin. Le caddie a une roue qui chante. L'air du magasin est un peu froid. Mila, tu tiens ma main ? Oui, maman. Bravo. Un bruit fort claque au fond. Mila sent encore son ventre. Le ventre se serre. Mila a peur. Elle se souvient. Elle marche vers maman. Maman, j'ai peur. Le bruit a été fort. Mon ventre est serré. Merci de raconter. Tu as repris le geste. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je suis là aussi. Je me sens plus légère. Bravo, Mila. La roue du caddie chante encore. Mila serre la main de maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lina joue au parc avec papa. Elle est près du bac à sable. Le sable est tiède. Un adulte parle tout bas. Il dit : c'est notre secret. Lina sent son ventre. C'est serré. C'est un malaise. Lina a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Lina marche vers papa. Elle prend sa main. Lina dit : papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Papa l'écoute. Papa dit : merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. Même si un adulte parle d'un secret. On va raconter à papa ou maman. Papa reste tout près. Plus tard, ils vont au magasin. Maman est là aussi. Lina sent encore son ventre. Un bruit fort la surprend. Elle a peur. Elle se souvient. Elle marche vers maman. Elle dit : maman, j'ai peur. Maman écoute. Maman dit : tu as repris le geste. Ce qui fait peur se raconte à papa ou maman. Lina se sent plus légère.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une feuille jaune colle à une chaussure. Elle est un peu humide. Une flaque garde un bout de ciel. Un nuage y passe tout lent. Le banc du parc est tiède. Un foulard bleu y dort. La terre mouillée sent fort. Mila, on enlève la feuille ? Elle colle encore. Voilà. Elle est partie. En ce moment, Mila est près du bac. Le sable est frais après la pluie. Elle fait un petit tas. Il est froid, papa. Oui. On reste ensemble. Une voix d'adulte parle tout bas. Mila sent son ventre. Le ventre est serré. C'est un malaise. Mila a peur. Elle laisse le tas de sable. Elle marche vers papa. Elle prend sa main. Papa, un adulte a parlé d'un secret. Mon ventre est serré. J'ai peur. Merci de raconter. Tu as le droit de le dire. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je reste tout près. On reste près ? Oui, Mila. Bravo. La feuille jaune s'envole un peu. Plus tard, ils vont au magasin. Le caddie a une roue qui chante. L'air du magasin est un peu froid. Mila, tu tiens ma main ? Oui, maman. Bravo. Un bruit fort claque au fond. Mila sent encore son ventre. Le ventre se serre. Mila a peur. Elle se souvient. Elle marche vers maman. Maman, j'ai peur. Le bruit a été fort. Mon ventre est serré. Merci de raconter. Tu as repris le geste. Ce qui fait peur se raconte. On va raconter à papa ou maman. Je suis là aussi. Je me sens plus légère. Bravo, Mila. La roue du caddie chante encore. Mila serre la main de maman.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1360,7 +1360,6 @@
 enfant-f|On reste près ?
 papa|Oui, Mila.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|La feuille jaune s'envole un peu.
 narrateur|Plus tard, ils vont au magasin.
 narrateur|Le caddie a une roue qui chante.
@@ -1384,7 +1383,6 @@
 papa|Je suis là aussi.
 enfant-f|Je me sens plus légère.
 maman|Bravo, Mila.
-maman|Tu as fait du bon travail.
 narrateur|La roue du caddie chante encore.
 narrateur|Mila serre la main de maman.</t>
         </is>
@@ -1423,7 +1421,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lina a &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt;. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a peur. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1582,7 +1580,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1612,7 +1609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lina a senti le malaise. Elle a marché vers papa, puis vers maman. Elle a raconté. Ce qui fait &lt;emphasis level="moderate"&gt;peur&lt;/emphasis&gt; se raconte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a senti le malaise. Elle a marché vers papa. Puis vers maman. Elle a raconté. Tu as raconté au parc ? Oui. Et au magasin aussi. Bravo. Ce qui fait peur se raconte. On va raconter à papa ou maman. La feuille jaune n'est plus collée. La main de maman reste chaude.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1765,7 +1762,6 @@
 narrateur|La main de maman reste chaude.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1790,12 +1786,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mila s'assoit près de maman. Papa pose un sac tout doux. On a fini les courses. Tu as raconté deux fois. Oui. Au parc, puis ici. Bravo. Tu as fait du bon travail. Le caddie s'arrête. La roue se tait. On rentre maintenant. On se tient la main.</t>
+          <t>Mila s'assoit près de maman. Papa pose un sac tout doux. On a fini les courses. Tu as raconté deux fois. Oui. Au parc, puis ici. Bravo. Le caddie s'arrête. La roue se tait. On rentre maintenant. On se tient la main.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lina s'assoit près de maman. Papa est là aussi. Sa &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; est chaude.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila s'assoit près de maman. Papa pose un sac tout doux. On a fini les courses. Tu as raconté deux fois. Oui. Au parc, puis ici. Bravo. Le caddie s'arrête. La roue se tait. On rentre maintenant. On se tient la main.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1937,14 +1933,12 @@
 enfant-f|Oui.
 enfant-f|Au parc, puis ici.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Le caddie s'arrête.
 narrateur|La roue se tait.
 papa|On rentre maintenant.
 enfant-f|On se tient la main.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La feuille jaune a séché dehors. J'ai raconté. Bravo, Mila. On t'écoute. L'histoire est finie.</t>
+          <t>La feuille jaune a séché dehors. J'ai raconté. Bravo, Mila. On t'écoute.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La feuille jaune a séché dehors. J'ai raconté. Bravo, Mila. On t'écoute.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2112,11 +2106,9 @@
           <t>narrateur|La feuille jaune a séché dehors.
 enfant-f|J'ai raconté.
 papa|Bravo, Mila.
-maman|On t'écoute.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|On t'écoute.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2135,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2180,6 +2172,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.002-02.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.002-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lina, papa, maman</t>
+          <t>Mila, papa, maman</t>
         </is>
       </c>
     </row>
